--- a/UTCUTS/B1_Model_Structure.xlsx
+++ b/UTCUTS/B1_Model_Structure.xlsx
@@ -7621,7 +7621,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E552EDEC-00A5-47EC-8598-F0EA8D02C8FE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B58D5C1-7443-4948-A6C2-1613159A050E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
